--- a/data/trans_orig/IP2901-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>50090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81924</t>
+          <t>81600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95120</t>
+          <t>94527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,89%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33097</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>37505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46177</t>
+          <t>46018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66551</t>
+          <t>66580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74297</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>64170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79904</t>
+          <t>79628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126392</t>
+          <t>128199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148440</t>
+          <t>149115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>28141</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55761</t>
+          <t>55214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48346</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59114</t>
+          <t>59122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96731</t>
+          <t>96751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111971</t>
+          <t>112169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56827</t>
+          <t>58528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68003</t>
+          <t>68302</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54208</t>
+          <t>53841</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66052</t>
+          <t>65834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116019</t>
+          <t>116223</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131661</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>21510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31269</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35514</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64730</t>
+          <t>64790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42509</t>
+          <t>43091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50662</t>
+          <t>50708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45875</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>54152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>91672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103050</t>
+          <t>103367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>46573</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16587</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97283</t>
+          <t>98173</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111308</t>
+          <t>111005</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>89351</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105295</t>
+          <t>105258</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>191558</t>
+          <t>192276</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>213409</t>
+          <t>213566</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>49799</t>
+          <t>48711</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42380</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62613</t>
+          <t>63103</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87659</t>
+          <t>87977</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>98460</t>
+          <t>97985</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116232</t>
+          <t>115850</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>104635</t>
+          <t>103030</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>122216</t>
+          <t>122385</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>206159</t>
+          <t>207901</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>233624</t>
+          <t>232944</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>105748</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>135276</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>150193</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>230396</t>
+          <t>232945</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>275478</t>
+          <t>278081</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>60056</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>73828</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>101346</t>
+          <t>103102</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>492897</t>
+          <t>494202</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>528087</t>
+          <t>527609</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>506028</t>
+          <t>506989</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>542538</t>
+          <t>544127</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1013630</t>
+          <t>1010789</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1061918</t>
+          <t>1061822</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31132</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37750</t>
+          <t>38420</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47942</t>
+          <t>48010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>41486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53031</t>
+          <t>53060</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82489</t>
+          <t>82588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97771</t>
+          <t>98369</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44597</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80711</t>
+          <t>81881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48382</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65835</t>
+          <t>65313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54535</t>
+          <t>55032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71941</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108976</t>
+          <t>107249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131936</t>
+          <t>132673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47444</t>
+          <t>48200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58840</t>
+          <t>59436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>42070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>55047</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93735</t>
+          <t>93412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111041</t>
+          <t>111019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>37853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>51033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64089</t>
+          <t>63474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66056</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108439</t>
+          <t>108575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127118</t>
+          <t>127081</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>44500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>37092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52260</t>
+          <t>52405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>461</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>43560</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53072</t>
+          <t>53126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85673</t>
+          <t>86465</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99526</t>
+          <t>100290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14213</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51870</t>
+          <t>51552</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30579</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98670</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114728</t>
+          <t>114901</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>104641</t>
+          <t>104115</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>120263</t>
+          <t>119863</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>207735</t>
+          <t>206781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230869</t>
+          <t>231262</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32727</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50629</t>
+          <t>50195</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45274</t>
+          <t>46442</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>83441</t>
+          <t>84186</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>111494</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>26998</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>41934</t>
+          <t>41277</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>98481</t>
+          <t>98774</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118344</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>81494</t>
+          <t>81304</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>102169</t>
+          <t>102738</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>187028</t>
+          <t>186094</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>215964</t>
+          <t>214815</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,24%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>133694</t>
+          <t>134541</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169164</t>
+          <t>170311</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>168476</t>
+          <t>168533</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>208834</t>
+          <t>209425</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>313820</t>
+          <t>313839</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>366123</t>
+          <t>365110</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>73597</t>
+          <t>73146</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>101428</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>137235</t>
+          <t>137365</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>477575</t>
+          <t>479691</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>516583</t>
+          <t>518918</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>473417</t>
+          <t>470960</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>516590</t>
+          <t>513957</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>961303</t>
+          <t>961615</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1020206</t>
+          <t>1020835</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29522</t>
+          <t>29656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42867</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53825</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80768</t>
+          <t>80937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96292</t>
+          <t>96608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44871</t>
+          <t>44661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>21982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>54908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76880</t>
+          <t>77610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68097</t>
+          <t>68828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63726</t>
+          <t>64555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79645</t>
+          <t>80702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121409</t>
+          <t>121696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143964</t>
+          <t>144814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47286</t>
+          <t>47666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59042</t>
+          <t>58850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>97050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113112</t>
+          <t>113209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54650</t>
+          <t>54427</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66816</t>
+          <t>67160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59382</t>
+          <t>59386</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71230</t>
+          <t>70818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>119044</t>
+          <t>118047</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135953</t>
+          <t>135299</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37176</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35643</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>40522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70088</t>
+          <t>69590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77200</t>
+          <t>76965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33616</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46004</t>
+          <t>45552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72181</t>
+          <t>72072</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87380</t>
+          <t>87584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>34437</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90946</t>
+          <t>91585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107248</t>
+          <t>107628</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>104308</t>
+          <t>104590</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>120448</t>
+          <t>120242</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>201552</t>
+          <t>200702</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>223246</t>
+          <t>223159</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34630</t>
+          <t>34313</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54069</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12319</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>123406</t>
+          <t>123295</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>138380</t>
+          <t>138206</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>125682</t>
+          <t>124831</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>140718</t>
+          <t>140677</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>252361</t>
+          <t>253687</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>274859</t>
+          <t>274599</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>125865</t>
+          <t>125738</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>82312</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>111990</t>
+          <t>112009</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>183535</t>
+          <t>185984</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>228850</t>
+          <t>226982</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>46206</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>103674</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>139203</t>
+          <t>137127</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>503032</t>
+          <t>500158</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>537980</t>
+          <t>537504</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>547655</t>
+          <t>548146</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>584137</t>
+          <t>584236</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1061791</t>
+          <t>1062684</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1112951</t>
+          <t>1111404</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
